--- a/AAII_Financials/Quarterly/HSBC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSBC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="92">
   <si>
     <t>HSBC</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18066000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17323000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14263000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16780000</v>
       </c>
-      <c r="G8" s="3">
-        <v>15408000</v>
-      </c>
       <c r="H8" s="3">
+        <v>14408000</v>
+      </c>
+      <c r="I8" s="3">
         <v>16773000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9002000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16012000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16194000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20032000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5732000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15090000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15792000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19739000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33038000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8006000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19788000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6475000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18228000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6610000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17960000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6514000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18756000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6450000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23000000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7612000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26945000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7568000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27750000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7468000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26187000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7680000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23422000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7456000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21268000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7127000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>19727000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6787000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>19403000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>7185000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18066000</v>
+      </c>
+      <c r="E10" s="3">
         <v>17323000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14263000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16780000</v>
       </c>
-      <c r="G10" s="3">
-        <v>15408000</v>
-      </c>
       <c r="H10" s="3">
+        <v>14408000</v>
+      </c>
+      <c r="I10" s="3">
         <v>16773000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9002000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16012000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16194000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20032000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5732000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15090000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15792000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19739000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,52 +1467,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E14" s="3">
         <v>178000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>205000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-50000</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="I14" s="3">
         <v>182000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1123000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-7000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>53000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3171000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-29000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-343000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,130 +1592,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>352800</v>
+        <v>1228000</v>
       </c>
       <c r="E15" s="3">
         <v>352800</v>
       </c>
       <c r="F15" s="3">
+        <v>352800</v>
+      </c>
+      <c r="G15" s="3">
         <v>324300</v>
       </c>
-      <c r="G15" s="3">
-        <v>1097500</v>
-      </c>
       <c r="H15" s="3">
-        <v>325800</v>
+        <v>1112500</v>
       </c>
       <c r="I15" s="3">
         <v>325800</v>
       </c>
       <c r="J15" s="3">
+        <v>325800</v>
+      </c>
+      <c r="K15" s="3">
         <v>302800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1007500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>302800</v>
       </c>
       <c r="M15" s="3">
         <v>302800</v>
       </c>
       <c r="N15" s="3">
+        <v>302800</v>
+      </c>
+      <c r="O15" s="3">
         <v>421500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>795500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>421500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1956000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>-1894000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>-1897000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>-1802000</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-2146000</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-3054000</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-1648000</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-1522000</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-987000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-946000</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-999000</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-863000</v>
       </c>
-      <c r="AN15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="3">
         <v>-999000</v>
       </c>
-      <c r="AP15" s="3" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7449000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8543000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6385000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10076000</v>
       </c>
-      <c r="G17" s="3">
-        <v>8970000</v>
-      </c>
       <c r="H17" s="3">
+        <v>7488000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8264000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6369000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8143000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6629000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8565000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6446000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7997000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8214000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7586000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18543000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1068000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7490000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>639000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4628000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-659000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4143000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-435000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7646000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>785000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>15349000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3026000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13339000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>883000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13650000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>585000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12158000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>507000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8729000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>170000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7975000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>448000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6613000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>236000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6384000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>566000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10617000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8780000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7878000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6704000</v>
       </c>
-      <c r="G18" s="3">
-        <v>6438000</v>
-      </c>
       <c r="H18" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="I18" s="3">
         <v>8509000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2633000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7869000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9565000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11467000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-714000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7093000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7578000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12153000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14495000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6938000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12298000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5836000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13600000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7269000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13817000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6949000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11110000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5665000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7651000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4586000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13606000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6685000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14100000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6883000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14029000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7173000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>14693000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7286000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>13293000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>6679000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>13114000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6551000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>13019000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>6619000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,252 +2056,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>649000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-774000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>871000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-591000</v>
       </c>
-      <c r="G20" s="3">
-        <v>162000</v>
-      </c>
       <c r="H20" s="3">
+        <v>776000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1157000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1479000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-607000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>666000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1236000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1480000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-592000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-850000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-733000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6217000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3709000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3518000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1692000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5533000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1866000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2978000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1170000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6651000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2591000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3333000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1357000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12666000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1848000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1693000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-670000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4851000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3981000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2531000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-6369000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2059000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2871000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1590000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-15621000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-5776000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11196000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9906800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7359800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7619300</v>
       </c>
-      <c r="G21" s="3">
-        <v>7373500</v>
-      </c>
       <c r="H21" s="3">
+        <v>7256500</v>
+      </c>
+      <c r="I21" s="3">
         <v>9991800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1479800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8778800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9906500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13005800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1891300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8106500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9223500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13307500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12128000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>12353000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>9700000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>9937000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>13929000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>10165000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>11658000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>7923000</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>11106000</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP21" s="3">
         <v>1603000</v>
       </c>
-      <c r="AP21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10146000</v>
+      </c>
+      <c r="E23" s="3">
         <v>9376000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6802000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7295000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6326000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9484000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2277000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8476000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8906000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12650000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>977000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7714000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8771000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12886000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8278000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3229000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8780000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4144000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8067000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5403000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10839000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5779000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4459000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3074000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4318000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3229000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>940000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4837000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12407000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6213000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9178000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5922000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10712000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4755000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6924000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4620000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>10243000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4961000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2602000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2219000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1982000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1615000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1792000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1455000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1914000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1692000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1727000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2078000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1813000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>755000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1448000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1726000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1860000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>960000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>572000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-151000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>712000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1796000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1161000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2417000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1211000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1485000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1035000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1193000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>721000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2169000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1042000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2470000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1303000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2569000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1406000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1017000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1805000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1115000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2195000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1201000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1375000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>803000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7394000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5187000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5503000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4871000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7570000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>585000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6749000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6828000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10837000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>222000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6266000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7045000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11026000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7318000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2657000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8931000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3432000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6271000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4242000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8422000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4568000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2974000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2039000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3125000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2508000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1229000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3795000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9937000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4910000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6609000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4516000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8416000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3738000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5119000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3505000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>8048000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3760000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-3977000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7345000</v>
+        <v>-6938000</v>
       </c>
       <c r="E27" s="3">
+        <v>6938000</v>
+      </c>
+      <c r="F27" s="3">
         <v>4719000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4873000</v>
       </c>
-      <c r="G27" s="3">
-        <v>4578000</v>
-      </c>
       <c r="H27" s="3">
-        <v>7324000</v>
+        <v>-6932000</v>
       </c>
       <c r="I27" s="3">
+        <v>6932000</v>
+      </c>
+      <c r="J27" s="3">
         <v>197000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6134000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6403000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10183000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-153000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5619000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6639000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10327000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6380000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2002000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7966000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2755000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5331000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3543000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7276000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3880000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1921000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1359000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1977000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2538000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2971000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8507000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5435000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3899000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7173000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3086000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3972000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2958000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>6999000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3130000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-5057000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-617000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1288000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-649000</v>
+      </c>
+      <c r="E32" s="3">
         <v>774000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-871000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>591000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-162000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-776000</v>
+      </c>
+      <c r="I32" s="3">
         <v>1157000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1479000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>607000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-666000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1236000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1480000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>592000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>850000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>733000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6217000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3709000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3518000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1692000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5533000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1866000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2978000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1170000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6651000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2591000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3333000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1357000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12666000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1848000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1693000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>670000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4851000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1251000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3981000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2531000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>6369000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2059000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2871000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1590000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>15621000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>5776000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7914000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7345000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4944000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5284000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4733000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7324000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>351000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6516000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6528000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10584000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6053000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6763000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10745000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6380000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2002000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7966000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2755000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5331000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3543000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7276000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3880000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1921000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1359000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1977000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2538000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2971000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8507000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5435000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3899000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7173000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3086000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2684000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2958000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>6999000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3130000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-5057000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-617000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7914000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7345000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4944000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5284000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4733000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7324000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>351000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6516000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6528000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10584000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6053000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6763000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10745000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6380000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2002000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7966000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2755000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5331000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3543000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7276000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3880000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1921000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1359000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1977000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2538000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2971000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8507000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5435000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3899000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7173000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3086000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2684000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2958000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>6999000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3130000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-5057000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-617000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>227800000</v>
+      </c>
+      <c r="E41" s="3">
         <v>214707000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>250663000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>246821000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>246360000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>254660000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>287077000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>252310000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>277112000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>275943000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>300688000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>298779000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>307733000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>327554000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>543249000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>408528000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>468110000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>479418000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>490290000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>512276000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>489851000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>473483000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>390191000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>369362000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>332977000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>271933000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>228258000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>221984000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>262160000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>244312000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>240797000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>251057000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>281847000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>263172000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>277645000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>252265000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>257115000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>220258000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>221138000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>215849000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>991853000</v>
+      </c>
+      <c r="E42" s="3">
         <v>948114000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>910454000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>849936000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>866621000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>810943000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>843099000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>845730000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>780765000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>801749000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>776956000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>771351000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>786038000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>726317000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>919528000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>878222000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>770597000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>745501000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>779347000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>715010000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>720600000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>727168000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>875440000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>782465000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>790875000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>850341000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>781755000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>784097000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>779167000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>743860000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>763072000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>721003000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>724646000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>752225000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>738830000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>770091000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>774527000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>748385000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>711727000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>845010000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1199000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1008000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>864000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>743000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1364000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1270000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1313000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1212000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1308000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1359000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1536000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1090000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1262000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1066000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,52 +4774,55 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22732000</v>
+      </c>
+      <c r="E45" s="3">
         <v>11583000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75993000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46026000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38978000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28131000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63125000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9182000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5821000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>167030000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>95480000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1465057000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1389191000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1378058000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1356146000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1357693000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1275261000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1318283000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1297279000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1249309000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1277474000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1378922000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1349019000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1365986000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1322248000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,202 +5024,208 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>820055000</v>
+      </c>
+      <c r="E47" s="3">
         <v>794433000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>765745000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>769945000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>747691000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>714416000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>673066000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>688523000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>655861000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>641705000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>616908000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>601540000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>584189000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>567112000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29254000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>29446000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>29609000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>28561000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>28709000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>27543000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>26684000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>24800000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>24474000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>23892000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>22407000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>22572000</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>22744000</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="3">
         <v>21071000</v>
       </c>
-      <c r="AN47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP47" s="3">
         <v>20029000</v>
       </c>
-      <c r="AP47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>12606000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>11612000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>12934000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>12584000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>13240000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>14414000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5137,160 +5244,166 @@
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>10060000</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>10027000</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AN48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP48" s="3">
         <v>9373000</v>
       </c>
-      <c r="AP48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12728000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12804000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13107000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13011000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13022000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12436000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12384000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12582000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12161000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12259000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12487000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12082000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11925000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11604000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21319000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>21625000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>20622000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20895000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20703000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>20275000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>20443000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>19438000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>20163000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>25733000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>24357000</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>23722000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>23453000</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>22653000</v>
       </c>
-      <c r="AN49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP49" s="3">
         <v>21346000</v>
       </c>
-      <c r="AP49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>33826000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>31968000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7513000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9977000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6766000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34855000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6698000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10649000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6577000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>131561000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24901000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5650000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>18304000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4572000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4615000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4450000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15232000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>4153000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>4632000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>4412000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>13119000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>4740000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>14209000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>669000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>8272000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2925000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>15266000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2036000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3438161000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3306011000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3233034000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3234223000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3214371000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3054361000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3017048000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3098621000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2975003000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3000517000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3038677000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3020611000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3041476000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2989696000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2949286000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2991965000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2985420000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3021512000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2957939000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2968791000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2976005000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2958629000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2984164000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2955935000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2922798000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2917810000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2715152000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2728347000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2751273000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2658996000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2558124000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2603035000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2607314000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2652123000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2521771000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2526214000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2492443000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2416467000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2374986000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2557261000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1919104000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1869342000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1912271000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1835373000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1816386000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1754671000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1752725000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1750052000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1676269000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1648146000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1705853000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1635346000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1664478000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1679612000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>254662000</v>
+      </c>
+      <c r="E58" s="3">
         <v>259845000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500670000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>217438000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>257601000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>212584000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>512668000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>239836000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>217096000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>231218000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>477079000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>265679000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>269560000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>237493000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>165042000</v>
+      </c>
+      <c r="E59" s="3">
         <v>148899000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>203445000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>173040000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>162642000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>147391000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>197055000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>138456000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138841000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>130278000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>283189000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>131218000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>223573000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129361000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13488000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>164285000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>11164000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>166003000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165729000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>159927000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11096000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>174322000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>120306000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>153705000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>98098000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>136383000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>45549000</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>43910000</v>
       </c>
-      <c r="AN59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP59" s="3">
         <v>42220000</v>
       </c>
-      <c r="AP59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2522929000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2462334000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2632529000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2405416000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2403691000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2266034000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2478725000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2282718000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2189377000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2178892000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2482935000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2281980000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2312886000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2279949000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>582916000</v>
+      </c>
+      <c r="E61" s="3">
         <v>513608000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>199236000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>504976000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>488819000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>474524000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>175885000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>479710000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>467238000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>498089000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>166757000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>432752000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>418485000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>394635000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100439000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>87527000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>108655000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>85330000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>102630000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>103406000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>104992000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>116856000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>122057000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>102406000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>133735000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>99410000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>129155000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>98486000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>126557000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>99038000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>107779000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>82095000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>104312000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>71482000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>213755000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>59740000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>84502000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>66877000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>200250000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>71650000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>132995000</v>
+      </c>
+      <c r="E62" s="3">
         <v>131079000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>192432000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>123603000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>120422000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>114268000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>167831000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>134666000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>126788000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>124041000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>193977000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>114587000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>117478000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>116467000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>118623000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>4794000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>17851000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6484000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7152000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6975000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10016000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>7700000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>6773000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>5845000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5539000</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>6382000</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>7279000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1093000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6885000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2114000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9186000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>853000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3241080000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3108741000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3027368000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3035535000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3014502000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2856244000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2824775000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2898596000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2784589000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2802140000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2846067000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2830771000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2849825000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2792173000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2771453000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2814306000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2797038000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2825219000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2759689000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2770647000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2777787000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2759419000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2787721000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2764031000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2735762000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2728039000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2531197000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2538830000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2558597000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2470634000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2371871000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2417684000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2423707000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2456199000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2331521000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2335201000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2304047000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2237683000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2199600000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2369153000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7540,19 +7707,19 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>19746000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>21691000</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
-        <v>22414000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>22414000</v>
@@ -7561,64 +7728,67 @@
         <v>22414000</v>
       </c>
       <c r="X70" s="3">
+        <v>22414000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>24414000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>22414000</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>20914000</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>20871000</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>22367000</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
         <v>22367000</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>20573000</v>
       </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
       <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
         <v>22250000</v>
       </c>
-      <c r="AL70" s="3">
-        <v>0</v>
-      </c>
       <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
         <v>20830000</v>
       </c>
-      <c r="AN70" s="3">
-        <v>0</v>
-      </c>
       <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
         <v>17110000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>167586000</v>
+      </c>
+      <c r="E72" s="3">
         <v>169597000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>169605000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>166315000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>149737000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>156701000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>152402000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>157149000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>155280000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>160309000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>152148000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>151954000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>149903000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>152791000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>166487000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>141841000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>174518000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>150753000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>150828000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>149833000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>167507000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>141508000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>164049000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>172370000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>167968000</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>168216000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>167307000</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN72" s="3">
         <v>168145000</v>
       </c>
-      <c r="AN72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP72" s="3">
         <v>163626000</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196682000</v>
+      </c>
+      <c r="E76" s="3">
         <v>196819000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>198225000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>191430000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>192554000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>190810000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>184973000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>192754000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183293000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>191186000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>185329000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>182720000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>184170000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>190095000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>158087000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177659000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>166691000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>196293000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>175836000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>175730000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>175804000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>174796000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>174029000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>191904000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>166122000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>189771000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>163084000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>189517000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>170309000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>188362000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>163886000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>185351000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>163034000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>195924000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>168000000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>191013000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>167566000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>178784000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>158276000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>188108000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7914000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7345000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4944000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5284000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4733000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7324000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>351000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6516000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6528000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10584000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6053000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6763000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10745000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6380000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2002000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7966000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2755000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5331000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3543000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7276000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3880000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1921000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1359000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1977000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2538000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2971000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8507000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5435000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3899000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7173000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3086000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2684000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2958000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>6999000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3130000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-5057000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-617000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,86 +9006,89 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>3873000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>4286000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>5241000</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>8997000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1522000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>987000</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>946000</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>999000</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>863000</v>
       </c>
-      <c r="AN83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AO83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ83" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,8 +9709,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9540,86 +9756,89 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>26434000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>104312000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>182220000</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-10792000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>40535000</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>24810000</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>7705000</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>1404000</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>-11882000</v>
       </c>
-      <c r="AN89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP89" s="3">
         <v>-6079000</v>
       </c>
-      <c r="AP89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,86 +9926,89 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1386000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2106000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1404000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1446000</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-811000</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-532000</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-676000</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-853000</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-314000</v>
       </c>
-      <c r="AN91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="AP91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,8 +10254,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10072,86 +10301,89 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-27401000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>27536000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-22430000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-4033000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-31285000</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-17642000</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>1301000</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>2835000</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>62722000</v>
       </c>
-      <c r="AN94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-1665000</v>
       </c>
-      <c r="AP94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,12 +10471,12 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-6970000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -10251,11 +10484,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-6383000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10263,11 +10496,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2023000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10275,49 +10508,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-5502000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4271000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-5797000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4965000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-5739000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-3266000</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-5428000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,8 +10924,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10726,86 +10971,89 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-6286000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-10794000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-4643000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-6460000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-8382000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-4925000</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-11856000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-9342000</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-1108000</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP100" s="3">
         <v>-4617000</v>
       </c>
-      <c r="AP100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,86 +11096,89 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-38029000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-15345000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>19434000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1294000</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-4262000</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-5415000</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>6687000</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>11546000</v>
       </c>
-      <c r="AN101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-12842000</v>
       </c>
-      <c r="AP101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10970,82 +11221,85 @@
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>-52361000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>105709000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>174581000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-19991000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>822000</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-1796000</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-9011000</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>1584000</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>61278000</v>
       </c>
-      <c r="AN102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-25203000</v>
       </c>
-      <c r="AP102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
